--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_31_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_31_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1902</v>
+        <v>5.946</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4148</v>
+        <v>3.6074</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7755</v>
+        <v>2.3386</v>
       </c>
       <c r="G2" t="n">
         <v>0.3124</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.4195</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0633</v>
+        <v>0.2559</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6005</v>
+        <v>0.1637</v>
       </c>
       <c r="V2" t="n">
         <v>3.3584</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5315</v>
+        <v>5.3121</v>
       </c>
       <c r="E3" t="n">
-        <v>2.846</v>
+        <v>2.4922</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6855</v>
+        <v>2.8199</v>
       </c>
       <c r="G3" t="n">
         <v>2.2742</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0975</v>
+        <v>-0.1219</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2715</v>
+        <v>-0.0824</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.174</v>
+        <v>-0.0395</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4917</v>
+        <v>2.8758</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9291</v>
+        <v>1.414</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5626</v>
+        <v>1.4618</v>
       </c>
       <c r="G4" t="n">
         <v>0.4198</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3245</v>
+        <v>0.7086</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9164</v>
+        <v>0.4013</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4081</v>
+        <v>0.3073</v>
       </c>
       <c r="V4" t="n">
         <v>0.8197</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3707</v>
+        <v>2.6044</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6084</v>
+        <v>1.8758</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7622</v>
+        <v>0.7286</v>
       </c>
       <c r="G5" t="n">
         <v>1.4574</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6814</v>
+        <v>0.9151</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2794</v>
+        <v>0.5467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.402</v>
+        <v>0.3684</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1261</v>
+        <v>1.3688</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2327</v>
+        <v>0.3074</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8933</v>
+        <v>1.0614</v>
       </c>
       <c r="G6" t="n">
         <v>0.1608</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4266</v>
+        <v>0.6693</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4955</v>
+        <v>0.5702</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.4665</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.838</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8035</v>
+        <v>-1.2137</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8837</v>
+        <v>2.0517</v>
       </c>
       <c r="G7" t="n">
         <v>0.2804</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.293</v>
+        <v>0.4648</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>0.3657</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0.7886</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2426</v>
+        <v>0.0008</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1625</v>
+        <v>0.1481</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0801</v>
+        <v>-0.1473</v>
       </c>
       <c r="G8" t="n">
         <v>0.3358</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2618</v>
+        <v>0.5052</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2161</v>
+        <v>0.0944</v>
       </c>
       <c r="U8" t="n">
-        <v>0.478</v>
+        <v>0.4107</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8689</v>
+        <v>-1.1742</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2128</v>
+        <v>-3.4173</v>
       </c>
       <c r="F9" t="n">
-        <v>2.344</v>
+        <v>2.2431</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2985</v>
@@ -1156,13 +1156,13 @@
         <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9116</v>
+        <v>0.6062</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8338</v>
+        <v>0.6293</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.0231</v>
       </c>
       <c r="V9" t="n">
         <v>0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0965</v>
+        <v>-2.7877</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0272</v>
+        <v>-0.8528</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0693</v>
+        <v>-1.9349</v>
       </c>
       <c r="G10" t="n">
         <v>0.1899</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8038</v>
+        <v>1.1125</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4312</v>
+        <v>0.6056</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3725</v>
+        <v>0.507</v>
       </c>
       <c r="V10" t="n">
         <v>-2.0026</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6775</v>
+        <v>-4.3322</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.924</v>
+        <v>-4.7131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2465</v>
+        <v>0.3809</v>
       </c>
       <c r="G11" t="n">
         <v>-2.213</v>
@@ -1312,13 +1312,13 @@
         <v>3.4793</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5316</v>
+        <v>0.8138</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7231</v>
+        <v>0.4878</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1915</v>
+        <v>0.326</v>
       </c>
       <c r="V11" t="n">
         <v>-2.933</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.9049</v>
+        <v>10.6518</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.099000000000001</v>
+        <v>-0.3520000000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>11.0039</v>
+        <v>11.0038</v>
       </c>
       <c r="G12" t="n">
         <v>2.9192</v>
@@ -1390,13 +1390,13 @@
         <v>18.5564</v>
       </c>
       <c r="S12" t="n">
-        <v>5.346399999999999</v>
+        <v>6.0931</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1279</v>
+        <v>3.8745</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2184</v>
+        <v>2.2187</v>
       </c>
       <c r="V12" t="n">
         <v>1.639399999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.846</v>
+        <v>1.6567</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6837</v>
+        <v>2.3902</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5297</v>
+        <v>-0.7335</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5215</v>
+        <v>0.1973</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6783</v>
+        <v>-0.8399</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8431999999999999</v>
+        <v>1.0372</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7608</v>
+        <v>1.7461</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6504</v>
+        <v>0.6554</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1104</v>
+        <v>1.0907</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7607</v>
+        <v>-1.5488</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0279</v>
+        <v>-1.4953</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7328</v>
+        <v>-0.0535</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0518</v>
+        <v>-0.7183</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7512</v>
+        <v>-0.4281</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.803</v>
+        <v>-0.2902</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2836</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6828</v>
+        <v>0.8996</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7239</v>
+        <v>1.1879</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4068</v>
+        <v>-0.2883</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1829</v>
+        <v>2.291</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9593</v>
+        <v>1.0698</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.1421</v>
+        <v>1.2212</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1506</v>
+        <v>3.0747</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8147</v>
+        <v>2.2183</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.6642</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3334</v>
+        <v>-0.7837</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8555</v>
+        <v>-1.1484</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5221</v>
+        <v>0.3648</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4411</v>
+        <v>-0.8011</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4604</v>
+        <v>-0.727</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9014</v>
+        <v>-0.074</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0026</v>
+        <v>-1.7501</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5616</v>
+        <v>0.8173</v>
       </c>
       <c r="E15" t="n">
-        <v>0.952</v>
+        <v>-1.1957</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3904</v>
+        <v>2.013</v>
       </c>
       <c r="G15" t="n">
-        <v>2.291</v>
+        <v>-0.1829</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0698</v>
+        <v>2.9593</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2212</v>
+        <v>-3.1421</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0747</v>
+        <v>0.1506</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2183</v>
+        <v>3.8147</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8564000000000001</v>
+        <v>-3.6642</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7837</v>
+        <v>-0.3334</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1484</v>
+        <v>-0.8555</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3648</v>
+        <v>0.5221</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3195</v>
+        <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1391</v>
+        <v>-0.3066</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>-0.0114</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1761</v>
+        <v>-0.2952</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7501</v>
+        <v>2.0026</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3485</v>
+        <v>0.4693</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5645</v>
+        <v>-1.5094</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.216</v>
+        <v>1.9787</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1973</v>
+        <v>2.5215</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8399</v>
+        <v>1.6783</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0372</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7461</v>
+        <v>1.7608</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6554</v>
+        <v>1.6504</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0907</v>
+        <v>0.1104</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5488</v>
+        <v>0.7607</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4953</v>
+        <v>0.0279</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0535</v>
+        <v>0.7328</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3195</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q16" t="n">
+        <v>-3.4793</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.4285</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.0745</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.3541</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.3195</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-2.0265</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-1.2538</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.7727000000000001</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.1418</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0403</v>
+        <v>-0.1697</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2943</v>
+        <v>-0.6481</v>
       </c>
       <c r="F17" t="n">
-        <v>0.254</v>
+        <v>0.4784</v>
       </c>
       <c r="G17" t="n">
         <v>-0.173</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3286</v>
+        <v>-0.458</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1098</v>
+        <v>-0.4637</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2188</v>
+        <v>0.0057</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6977</v>
+        <v>-0.6984</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2041</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4936</v>
+        <v>0.2134</v>
       </c>
       <c r="G18" t="n">
         <v>1.1879</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.177</v>
+        <v>-0.1777</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6097</v>
+        <v>-0.098</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>2.0026</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3035</v>
+        <v>-1.079</v>
       </c>
       <c r="E19" t="n">
         <v>0.9015</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.205</v>
+        <v>-1.9805</v>
       </c>
       <c r="G19" t="n">
         <v>-3.3824</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0808</v>
+        <v>0.1436</v>
       </c>
       <c r="T19" t="n">
         <v>0.13</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2109</v>
+        <v>0.0136</v>
       </c>
       <c r="V19" t="n">
         <v>0.5361</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7331</v>
+        <v>-2.3121</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3908</v>
+        <v>-2.037</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3423</v>
+        <v>-0.2751</v>
       </c>
       <c r="G20" t="n">
         <v>-1.866</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1713</v>
+        <v>0.2497</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2882</v>
+        <v>-3.1854</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.787</v>
+        <v>-6.0793</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4988</v>
+        <v>2.8939</v>
       </c>
       <c r="G21" t="n">
         <v>-1.528</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4586</v>
+        <v>-0.3558</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.187</v>
+        <v>-0.4793</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7284</v>
+        <v>0.1235</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2811</v>
+        <v>-3.9443</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.802</v>
+        <v>-2.5661</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.479</v>
+        <v>-1.3782</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9848</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4714</v>
+        <v>-0.1346</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0312</v>
+        <v>0.0696</v>
       </c>
       <c r="V22" t="n">
         <v>-3.2166</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.904999999999999</v>
+        <v>-7.545999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>-10.4678</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5630000000000006</v>
+        <v>2.9218</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9194</v>
@@ -2248,13 +2248,13 @@
         <v>18.5561</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.3462</v>
+        <v>-2.9873</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2186</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.1277</v>
+        <v>-0.7688</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6394</v>
